--- a/data/trans_orig/IMC_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IMC_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (recodificación OMS) en 2007</t>
+          <t>Índice de masa corporal (recodificación OMS) en 2007 (tasa de respuesta: 98,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40426</t>
+          <t>39679</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69537</t>
+          <t>69153</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9083</t>
+          <t>9183</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24357</t>
+          <t>25463</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54541</t>
+          <t>54128</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86924</t>
+          <t>87836</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>222878</t>
+          <t>223759</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>268892</t>
+          <t>267803</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57541</t>
+          <t>57693</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>87249</t>
+          <t>88274</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>291420</t>
+          <t>288455</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>342468</t>
+          <t>344377</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,53%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>147591</t>
+          <t>150002</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>191849</t>
+          <t>194559</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>183313</t>
+          <t>183826</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>216601</t>
+          <t>219206</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>347225</t>
+          <t>343867</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>400240</t>
+          <t>400783</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,82%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8983</t>
+          <t>7353</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24308</t>
+          <t>22740</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>8930</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24236</t>
+          <t>24813</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33651</t>
+          <t>32724</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59302</t>
+          <t>58998</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18260</t>
+          <t>18832</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39423</t>
+          <t>39185</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>56436</t>
+          <t>56621</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>89504</t>
+          <t>92158</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>151931</t>
+          <t>152697</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>191665</t>
+          <t>191249</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>83643</t>
+          <t>85470</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>117942</t>
+          <t>118535</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>246399</t>
+          <t>246812</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>302958</t>
+          <t>298314</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>40,81%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>126183</t>
+          <t>125561</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>163714</t>
+          <t>164247</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>213403</t>
+          <t>214911</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>250717</t>
+          <t>250358</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>345974</t>
+          <t>350455</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>404571</t>
+          <t>402747</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,09%</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>5833</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15865</t>
+          <t>15287</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16955</t>
+          <t>16280</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68882</t>
+          <t>68677</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100521</t>
+          <t>100839</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19906</t>
+          <t>21028</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40147</t>
+          <t>40265</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>95226</t>
+          <t>95544</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>133461</t>
+          <t>133107</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>253438</t>
+          <t>255057</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>299872</t>
+          <t>301192</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34348</t>
+          <t>33631</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56475</t>
+          <t>56660</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>296348</t>
+          <t>296170</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>348783</t>
+          <t>349835</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,48%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>157493</t>
+          <t>157430</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>200008</t>
+          <t>199047</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>73101</t>
+          <t>73711</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99194</t>
+          <t>99191</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>236609</t>
+          <t>241272</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>289200</t>
+          <t>290202</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,04%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>983</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9196</t>
+          <t>9264</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11258</t>
+          <t>10522</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14647</t>
+          <t>15462</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>139085</t>
+          <t>139682</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>186004</t>
+          <t>191555</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>77019</t>
+          <t>77488</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>116059</t>
+          <t>114470</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>228303</t>
+          <t>228818</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>288904</t>
+          <t>287182</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>588888</t>
+          <t>589321</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>660056</t>
+          <t>659044</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>192409</t>
+          <t>195030</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>244222</t>
+          <t>243829</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>803454</t>
+          <t>802658</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>892030</t>
+          <t>890531</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,0%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>402109</t>
+          <t>402084</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>470262</t>
+          <t>468536</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>349952</t>
+          <t>351355</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>405755</t>
+          <t>406101</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>768871</t>
+          <t>772349</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>851624</t>
+          <t>854710</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>44,15%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11854</t>
+          <t>12743</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11190</t>
+          <t>10920</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30059</t>
+          <t>28613</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14880</t>
+          <t>14498</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34916</t>
+          <t>35854</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30956</t>
+          <t>31518</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>54592</t>
+          <t>55551</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>89787</t>
+          <t>90619</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>127515</t>
+          <t>128398</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>127739</t>
+          <t>128928</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>175084</t>
+          <t>175485</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>128036</t>
+          <t>127767</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>164079</t>
+          <t>165457</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>183728</t>
+          <t>184295</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>230692</t>
+          <t>230621</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>322724</t>
+          <t>324879</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>381122</t>
+          <t>382075</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,42%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>132193</t>
+          <t>131511</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>169563</t>
+          <t>169038</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>214788</t>
+          <t>217178</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>260423</t>
+          <t>263830</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>358257</t>
+          <t>360298</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>422698</t>
+          <t>418070</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>46,42%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12002</t>
+          <t>12320</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10440</t>
+          <t>11129</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>18706</t>
+          <t>17861</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14181</t>
+          <t>15001</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>195085</t>
+          <t>196349</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>247955</t>
+          <t>248960</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>203876</t>
+          <t>203205</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>255686</t>
+          <t>257397</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>48973</t>
+          <t>48368</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>75282</t>
+          <t>75895</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>400411</t>
+          <t>401518</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>465257</t>
+          <t>470046</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>460275</t>
+          <t>462603</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>532025</t>
+          <t>529373</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,76%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>209447</t>
+          <t>207882</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>237882</t>
+          <t>236996</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>501445</t>
+          <t>498661</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>568263</t>
+          <t>569422</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>719383</t>
+          <t>719906</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>795363</t>
+          <t>793002</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,06%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>996</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9327</t>
+          <t>9739</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>26161</t>
+          <t>26438</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>51223</t>
+          <t>50165</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>27814</t>
+          <t>28950</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>53048</t>
+          <t>53763</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>358576</t>
+          <t>356159</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>432948</t>
+          <t>431372</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>459791</t>
+          <t>457272</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>536877</t>
+          <t>540897</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>840130</t>
+          <t>837635</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>955135</t>
+          <t>949672</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1468280</t>
+          <t>1470920</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1584987</t>
+          <t>1585275</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4295,12 +4295,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1023110</t>
+          <t>1025856</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1133539</t>
+          <t>1128622</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2530586</t>
+          <t>2527685</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2685660</t>
+          <t>2679374</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,12 +4345,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,78%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1241804</t>
+          <t>1246372</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1358886</t>
+          <t>1354987</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1606645</t>
+          <t>1614977</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1725340</t>
+          <t>1728903</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2889220</t>
+          <t>2889403</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3044004</t>
+          <t>3048150</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,39%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>11112</t>
+          <t>11399</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>28482</t>
+          <t>28557</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>71398</t>
+          <t>70189</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>106818</t>
+          <t>106372</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>87155</t>
+          <t>87288</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>127787</t>
+          <t>126105</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4755,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (recodificación OMS) en 2012</t>
+          <t>Índice de masa corporal (recodificación OMS) en 2012 (tasa de respuesta: 96,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4950,12 +4950,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40510</t>
+          <t>40100</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70288</t>
+          <t>69253</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4965,12 +4965,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>13550</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31046</t>
+          <t>32681</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5000,12 +5000,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60366</t>
+          <t>57681</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94467</t>
+          <t>91202</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5035,12 +5035,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -5063,12 +5063,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>206652</t>
+          <t>206489</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>249678</t>
+          <t>250053</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63884</t>
+          <t>63405</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>96513</t>
+          <t>94369</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5113,12 +5113,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>281002</t>
+          <t>279726</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>335968</t>
+          <t>334933</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,18%</t>
         </is>
       </c>
     </row>
@@ -5176,12 +5176,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>128524</t>
+          <t>128975</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>169917</t>
+          <t>170884</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5191,12 +5191,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>179986</t>
+          <t>178394</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>217111</t>
+          <t>215372</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>319152</t>
+          <t>315463</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>375745</t>
+          <t>373790</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5261,12 +5261,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,42%</t>
         </is>
       </c>
     </row>
@@ -5289,12 +5289,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>6661</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21465</t>
+          <t>21137</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5339,12 +5339,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>6994</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21070</t>
+          <t>22119</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5374,12 +5374,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48091</t>
+          <t>47721</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79113</t>
+          <t>78357</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26032</t>
+          <t>26157</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50255</t>
+          <t>49083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>79492</t>
+          <t>81184</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>118968</t>
+          <t>119617</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5604,12 +5604,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -5632,12 +5632,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>193006</t>
+          <t>193026</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>237229</t>
+          <t>235466</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82374</t>
+          <t>84567</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119040</t>
+          <t>122006</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>286085</t>
+          <t>287361</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>343142</t>
+          <t>344236</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5717,12 +5717,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>47,12%</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5745,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>105141</t>
+          <t>105674</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>146038</t>
+          <t>145227</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158463</t>
+          <t>155874</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>197986</t>
+          <t>194727</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>272483</t>
+          <t>271907</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>331216</t>
+          <t>332543</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,51%</t>
         </is>
       </c>
     </row>
@@ -5858,12 +5858,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>910</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8570</t>
+          <t>7865</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6705</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20934</t>
+          <t>20856</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9749</t>
+          <t>8719</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25377</t>
+          <t>24495</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5943,12 +5943,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -6088,12 +6088,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>109483</t>
+          <t>112221</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>153198</t>
+          <t>155512</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51718</t>
+          <t>49576</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79875</t>
+          <t>78233</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>169809</t>
+          <t>171761</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>220066</t>
+          <t>219818</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -6201,12 +6201,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>293370</t>
+          <t>293365</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>345993</t>
+          <t>343002</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>69986</t>
+          <t>68522</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>99183</t>
+          <t>100483</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>371971</t>
+          <t>372800</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>432353</t>
+          <t>435017</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>50,36%</t>
         </is>
       </c>
     </row>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>143476</t>
+          <t>142492</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>188709</t>
+          <t>188328</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>78822</t>
+          <t>78054</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>109616</t>
+          <t>109322</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>235162</t>
+          <t>233427</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>294092</t>
+          <t>288006</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,34%</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>980</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>7285</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11159</t>
+          <t>11081</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -6657,12 +6657,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>182047</t>
+          <t>182140</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>234069</t>
+          <t>234986</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>119397</t>
+          <t>118036</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>163385</t>
+          <t>161972</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>312472</t>
+          <t>316692</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>379746</t>
+          <t>383593</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6770,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>539472</t>
+          <t>532212</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>610909</t>
+          <t>604928</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>214291</t>
+          <t>214306</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>265980</t>
+          <t>268724</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>764582</t>
+          <t>772571</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>853894</t>
+          <t>857882</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,26%</t>
         </is>
       </c>
     </row>
@@ -6883,12 +6883,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>320220</t>
+          <t>321159</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>387031</t>
+          <t>387665</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>325331</t>
+          <t>324183</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>382421</t>
+          <t>378819</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>663107</t>
+          <t>664813</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>748142</t>
+          <t>751036</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,62%</t>
         </is>
       </c>
     </row>
@@ -6996,12 +6996,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4051</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15237</t>
+          <t>15658</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>12698</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31906</t>
+          <t>30912</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18966</t>
+          <t>19135</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41169</t>
+          <t>40733</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>75663</t>
+          <t>75214</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>108524</t>
+          <t>107861</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>171945</t>
+          <t>172910</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>219829</t>
+          <t>222238</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>259826</t>
+          <t>255065</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>319724</t>
+          <t>317857</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -7339,12 +7339,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>207556</t>
+          <t>211031</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>254107</t>
+          <t>256121</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>229835</t>
+          <t>228982</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>283367</t>
+          <t>283152</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>451652</t>
+          <t>452655</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>523080</t>
+          <t>523654</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,38%</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>149029</t>
+          <t>150098</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>191089</t>
+          <t>192281</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>225466</t>
+          <t>224016</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>280735</t>
+          <t>279573</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>388577</t>
+          <t>388565</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>455551</t>
+          <t>456430</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,81%</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>14411</t>
+          <t>15420</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>18141</t>
+          <t>17534</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18012</t>
+          <t>17234</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>229925</t>
+          <t>226839</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>287406</t>
+          <t>284351</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>239636</t>
+          <t>234410</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>296775</t>
+          <t>298606</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>61867</t>
+          <t>63021</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>91603</t>
+          <t>91121</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>337122</t>
+          <t>339435</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>400002</t>
+          <t>402929</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>406949</t>
+          <t>410097</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>480556</t>
+          <t>480137</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,42%</t>
         </is>
       </c>
     </row>
@@ -8021,12 +8021,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>146910</t>
+          <t>149655</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>180024</t>
+          <t>180484</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>367420</t>
+          <t>363361</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>429035</t>
+          <t>430478</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>524019</t>
+          <t>523270</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>595464</t>
+          <t>595362</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,15%</t>
         </is>
       </c>
     </row>
@@ -8134,12 +8134,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>8682</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>24522</t>
+          <t>24364</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>20334</t>
+          <t>19379</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>40604</t>
+          <t>42213</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>32667</t>
+          <t>32233</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>58118</t>
+          <t>57954</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>512324</t>
+          <t>512546</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>603293</t>
+          <t>602215</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>665071</t>
+          <t>663919</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>766973</t>
+          <t>766330</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1204201</t>
+          <t>1202580</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1335037</t>
+          <t>1337501</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,79%</t>
         </is>
       </c>
     </row>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1582900</t>
+          <t>1581675</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1705958</t>
+          <t>1701501</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1079160</t>
+          <t>1078847</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1189501</t>
+          <t>1189185</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2687561</t>
+          <t>2687612</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2850501</t>
+          <t>2858694</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,31%</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1068792</t>
+          <t>1074839</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1183274</t>
+          <t>1190701</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1412267</t>
+          <t>1409221</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1527983</t>
+          <t>1532551</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8640,12 +8640,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2516780</t>
+          <t>2516203</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2689761</t>
+          <t>2678114</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,64%</t>
         </is>
       </c>
     </row>
@@ -8703,12 +8703,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>21913</t>
+          <t>21490</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>44089</t>
+          <t>42745</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>66880</t>
+          <t>67235</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>103817</t>
+          <t>103928</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>94722</t>
+          <t>94418</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>136325</t>
+          <t>136191</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8972,7 +8972,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (recodificación OMS) en 2016</t>
+          <t>Índice de masa corporal (recodificación OMS) en 2016 (tasa de respuesta: 95,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9167,12 +9167,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55876</t>
+          <t>56275</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86865</t>
+          <t>87945</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9182,12 +9182,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25820</t>
+          <t>26156</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50243</t>
+          <t>50568</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9217,12 +9217,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>86629</t>
+          <t>87932</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>127919</t>
+          <t>129208</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9252,12 +9252,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -9280,12 +9280,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>159131</t>
+          <t>158261</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>201167</t>
+          <t>202184</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9295,12 +9295,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>82453</t>
+          <t>82190</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>117544</t>
+          <t>115608</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9330,12 +9330,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>252350</t>
+          <t>253432</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>305323</t>
+          <t>305544</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9365,12 +9365,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,23%</t>
         </is>
       </c>
     </row>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>150371</t>
+          <t>149433</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>191759</t>
+          <t>192412</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9408,12 +9408,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>173486</t>
+          <t>173659</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>208444</t>
+          <t>212071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>335857</t>
+          <t>334885</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>393742</t>
+          <t>391367</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,54%</t>
         </is>
       </c>
     </row>
@@ -9511,7 +9511,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11240</t>
+          <t>9885</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3907</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14638</t>
+          <t>15719</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5653</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20855</t>
+          <t>19107</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -9736,12 +9736,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40899</t>
+          <t>40431</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68049</t>
+          <t>67111</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9751,12 +9751,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9771,12 +9771,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25693</t>
+          <t>25170</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49543</t>
+          <t>49650</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9786,12 +9786,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9806,12 +9806,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>71213</t>
+          <t>72472</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>109516</t>
+          <t>110231</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9821,12 +9821,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -9849,12 +9849,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>147768</t>
+          <t>146858</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>186180</t>
+          <t>186893</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>93734</t>
+          <t>93233</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>128431</t>
+          <t>128056</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>247860</t>
+          <t>248533</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>303933</t>
+          <t>304700</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,83%</t>
         </is>
       </c>
     </row>
@@ -9962,12 +9962,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>124913</t>
+          <t>125424</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>163231</t>
+          <t>163411</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>193434</t>
+          <t>191423</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>231750</t>
+          <t>230325</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>329010</t>
+          <t>329705</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>387495</t>
+          <t>384786</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>52,83%</t>
         </is>
       </c>
     </row>
@@ -10075,12 +10075,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>916</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>9444</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>940</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8888</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2762</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13884</t>
+          <t>14286</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -10305,12 +10305,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71352</t>
+          <t>69784</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>105334</t>
+          <t>105093</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18302</t>
+          <t>18560</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38372</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>96763</t>
+          <t>96148</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -10418,12 +10418,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>219678</t>
+          <t>222267</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>264159</t>
+          <t>266174</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10433,12 +10433,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>51369</t>
+          <t>50685</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>77283</t>
+          <t>76507</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>279326</t>
+          <t>279782</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>331708</t>
+          <t>332455</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,45%</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>148792</t>
+          <t>149502</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>192139</t>
+          <t>192033</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50616</t>
+          <t>51327</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76001</t>
+          <t>76878</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>210953</t>
+          <t>210027</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>261374</t>
+          <t>262674</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,86%</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>7096</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10699,7 +10699,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>925</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8956</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -10874,12 +10874,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>186305</t>
+          <t>185212</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>244764</t>
+          <t>240205</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>102716</t>
+          <t>101568</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>144155</t>
+          <t>142377</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>299371</t>
+          <t>299510</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>366988</t>
+          <t>366580</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10959,12 +10959,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -10987,12 +10987,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>493017</t>
+          <t>486777</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>565027</t>
+          <t>559208</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>219152</t>
+          <t>217424</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273369</t>
+          <t>274200</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>726201</t>
+          <t>733534</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>818361</t>
+          <t>819219</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11072,12 +11072,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,32%</t>
         </is>
       </c>
     </row>
@@ -11100,12 +11100,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>331878</t>
+          <t>334711</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>397349</t>
+          <t>395194</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11135,12 +11135,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>354892</t>
+          <t>356932</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>413899</t>
+          <t>413949</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11150,7 +11150,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>708612</t>
+          <t>707366</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>793913</t>
+          <t>794500</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11185,12 +11185,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,02%</t>
         </is>
       </c>
     </row>
@@ -11213,12 +11213,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1808</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9857</t>
+          <t>11064</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22606</t>
+          <t>21372</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44399</t>
+          <t>44209</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11263,12 +11263,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26140</t>
+          <t>25592</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50459</t>
+          <t>50209</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11298,12 +11298,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -11443,12 +11443,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>99833</t>
+          <t>100871</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>141526</t>
+          <t>138999</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>145826</t>
+          <t>146939</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>190240</t>
+          <t>192181</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>258507</t>
+          <t>260657</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>318555</t>
+          <t>322762</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11528,12 +11528,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -11556,12 +11556,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>231201</t>
+          <t>231872</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>279264</t>
+          <t>279354</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11591,12 +11591,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>228813</t>
+          <t>228530</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>280066</t>
+          <t>280347</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11626,12 +11626,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>476668</t>
+          <t>472323</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>547061</t>
+          <t>543558</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,6%</t>
         </is>
       </c>
     </row>
@@ -11669,12 +11669,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>186357</t>
+          <t>186397</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>232955</t>
+          <t>232773</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11704,12 +11704,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>225170</t>
+          <t>226488</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>279078</t>
+          <t>274203</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11739,12 +11739,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>424163</t>
+          <t>426311</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>496579</t>
+          <t>492556</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11754,12 +11754,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,6%</t>
         </is>
       </c>
     </row>
@@ -11782,12 +11782,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10564</t>
+          <t>10963</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11802,7 +11802,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11817,12 +11817,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7544</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>23545</t>
+          <t>22680</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11852,12 +11852,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>10561</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>27655</t>
+          <t>27924</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11867,12 +11867,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -12012,12 +12012,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7350</t>
+          <t>7440</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22503</t>
+          <t>22914</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12027,12 +12027,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>203747</t>
+          <t>203829</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>259624</t>
+          <t>261928</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12082,12 +12082,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>216992</t>
+          <t>218099</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>276466</t>
+          <t>278687</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12097,12 +12097,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,74%</t>
         </is>
       </c>
     </row>
@@ -12125,12 +12125,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>46997</t>
+          <t>45979</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>72849</t>
+          <t>73784</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12160,12 +12160,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>311223</t>
+          <t>312246</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>369374</t>
+          <t>372208</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12195,12 +12195,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>368133</t>
+          <t>366679</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>435671</t>
+          <t>433071</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12210,12 +12210,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,78%</t>
         </is>
       </c>
     </row>
@@ -12238,12 +12238,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>177834</t>
+          <t>175848</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>206786</t>
+          <t>207932</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12273,12 +12273,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>371358</t>
+          <t>377969</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>436652</t>
+          <t>438847</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12308,12 +12308,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>561953</t>
+          <t>561045</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>637750</t>
+          <t>633731</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12323,12 +12323,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,43%</t>
         </is>
       </c>
     </row>
@@ -12351,12 +12351,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>6949</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>21438</t>
+          <t>20985</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>16210</t>
+          <t>16297</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>35968</t>
+          <t>36584</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>26366</t>
+          <t>26470</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>49749</t>
+          <t>50559</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -12581,12 +12581,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>513396</t>
+          <t>510748</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>601664</t>
+          <t>600139</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12616,12 +12616,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>580105</t>
+          <t>572289</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>675784</t>
+          <t>667846</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12651,12 +12651,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1116123</t>
+          <t>1113407</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1243288</t>
+          <t>1241707</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12666,12 +12666,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -12694,12 +12694,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1368379</t>
+          <t>1369640</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1485838</t>
+          <t>1486518</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12729,12 +12729,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1053719</t>
+          <t>1056893</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1166397</t>
+          <t>1171209</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12764,12 +12764,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2461349</t>
+          <t>2468526</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2624615</t>
+          <t>2631251</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12779,12 +12779,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,89%</t>
         </is>
       </c>
     </row>
@@ -12807,12 +12807,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1197156</t>
+          <t>1194130</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1310946</t>
+          <t>1307398</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12842,12 +12842,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1453894</t>
+          <t>1449382</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1567323</t>
+          <t>1571930</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12877,12 +12877,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2684394</t>
+          <t>2685383</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2850714</t>
+          <t>2841163</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12892,12 +12892,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,08%</t>
         </is>
       </c>
     </row>
@@ -12920,12 +12920,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>20065</t>
+          <t>20677</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>42644</t>
+          <t>42629</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -12955,12 +12955,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>65223</t>
+          <t>65677</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>101580</t>
+          <t>102115</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12990,12 +12990,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>89992</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>133637</t>
+          <t>136834</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13005,12 +13005,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -13189,7 +13189,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (recodificación OMS) en 2023</t>
+          <t>Índice de masa corporal (recodificación OMS) en 2023 (tasa de respuesta: 96,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13384,12 +13384,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52118</t>
+          <t>50881</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81818</t>
+          <t>80149</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13399,12 +13399,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31594</t>
+          <t>30810</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52196</t>
+          <t>52026</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13434,12 +13434,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>87888</t>
+          <t>88328</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>123912</t>
+          <t>123599</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13469,12 +13469,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -13497,12 +13497,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>203729</t>
+          <t>204917</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>247425</t>
+          <t>250777</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13512,12 +13512,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>95688</t>
+          <t>94688</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>125387</t>
+          <t>124914</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13547,12 +13547,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>306999</t>
+          <t>309166</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>363852</t>
+          <t>364048</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13582,12 +13582,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,03%</t>
         </is>
       </c>
     </row>
@@ -13610,12 +13610,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>183331</t>
+          <t>180518</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>226859</t>
+          <t>228008</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13625,12 +13625,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13645,12 +13645,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>262490</t>
+          <t>262175</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>296051</t>
+          <t>296738</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13660,12 +13660,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13680,12 +13680,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>458452</t>
+          <t>454561</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>513755</t>
+          <t>513686</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13695,7 +13695,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6615</t>
+          <t>6686</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13743,7 +13743,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13758,12 +13758,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10287</t>
+          <t>9026</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13773,12 +13773,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13793,12 +13793,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12682</t>
+          <t>12824</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13808,12 +13808,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -13953,12 +13953,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64694</t>
+          <t>63612</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>99823</t>
+          <t>100997</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -13968,12 +13968,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39462</t>
+          <t>38996</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58863</t>
+          <t>59760</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14003,12 +14003,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>110840</t>
+          <t>109140</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>152199</t>
+          <t>151808</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14038,12 +14038,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -14066,12 +14066,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>168317</t>
+          <t>166658</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>210538</t>
+          <t>210888</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14081,12 +14081,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14101,12 +14101,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>107306</t>
+          <t>107808</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>138828</t>
+          <t>138972</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14116,12 +14116,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14136,12 +14136,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>288037</t>
+          <t>285009</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>340074</t>
+          <t>340566</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14151,12 +14151,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,46%</t>
         </is>
       </c>
     </row>
@@ -14179,12 +14179,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>157542</t>
+          <t>156320</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>198750</t>
+          <t>201087</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14194,12 +14194,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14214,12 +14214,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>176826</t>
+          <t>177194</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>209458</t>
+          <t>210513</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14229,12 +14229,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14249,12 +14249,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>340958</t>
+          <t>340814</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>397349</t>
+          <t>398405</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14264,12 +14264,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,5%</t>
         </is>
       </c>
     </row>
@@ -14297,7 +14297,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14327,12 +14327,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5173</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16361</t>
+          <t>15927</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14342,12 +14342,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14362,12 +14362,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>5659</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17331</t>
+          <t>17423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14377,12 +14377,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -14522,12 +14522,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>129950</t>
+          <t>127383</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>544327</t>
+          <t>531117</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14537,12 +14537,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14557,12 +14557,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18979</t>
+          <t>18723</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32574</t>
+          <t>33258</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14572,12 +14572,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14592,12 +14592,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>151200</t>
+          <t>150544</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>608871</t>
+          <t>630048</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14607,12 +14607,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>76,76%</t>
         </is>
       </c>
     </row>
@@ -14635,12 +14635,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71829</t>
+          <t>79825</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>330537</t>
+          <t>331024</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -14650,12 +14650,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -14670,12 +14670,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>40442</t>
+          <t>40438</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57292</t>
+          <t>58700</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -14705,12 +14705,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>111788</t>
+          <t>106107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>366932</t>
+          <t>365804</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -14720,12 +14720,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,57%</t>
         </is>
       </c>
     </row>
@@ -14748,12 +14748,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41788</t>
+          <t>43651</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>205718</t>
+          <t>207053</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14763,12 +14763,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14783,12 +14783,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>71229</t>
+          <t>72426</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>91987</t>
+          <t>93027</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14798,12 +14798,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14818,12 +14818,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>94207</t>
+          <t>78910</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>303599</t>
+          <t>304092</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,05%</t>
         </is>
       </c>
     </row>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14896,12 +14896,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16148</t>
+          <t>17033</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -14911,12 +14911,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -14931,12 +14931,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18862</t>
+          <t>18507</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -14946,12 +14946,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>175046</t>
+          <t>179976</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>227225</t>
+          <t>232463</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15106,12 +15106,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15126,12 +15126,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>147740</t>
+          <t>147108</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>627333</t>
+          <t>621143</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15141,12 +15141,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15161,12 +15161,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>347780</t>
+          <t>345008</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>989000</t>
+          <t>958867</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15176,12 +15176,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>48,5%</t>
         </is>
       </c>
     </row>
@@ -15204,12 +15204,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>448631</t>
+          <t>451772</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>520369</t>
+          <t>522340</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15219,12 +15219,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15239,12 +15239,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>139131</t>
+          <t>142900</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>348919</t>
+          <t>349159</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15254,12 +15254,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15274,12 +15274,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>505868</t>
+          <t>495701</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>854543</t>
+          <t>856174</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15289,12 +15289,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,31%</t>
         </is>
       </c>
     </row>
@@ -15317,12 +15317,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>292309</t>
+          <t>288796</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>366290</t>
+          <t>358913</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15332,12 +15332,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15352,12 +15352,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>177137</t>
+          <t>187042</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>450919</t>
+          <t>449525</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15367,12 +15367,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15387,12 +15387,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>472854</t>
+          <t>475478</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>767191</t>
+          <t>769010</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15402,12 +15402,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,9%</t>
         </is>
       </c>
     </row>
@@ -15430,12 +15430,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>12551</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15450,7 +15450,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15465,12 +15465,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9809</t>
+          <t>9446</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31988</t>
+          <t>33040</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15500,12 +15500,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15668</t>
+          <t>15632</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37770</t>
+          <t>38599</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15520,7 +15520,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -15660,12 +15660,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>69949</t>
+          <t>69810</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>104531</t>
+          <t>104079</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15675,12 +15675,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15695,12 +15695,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>123167</t>
+          <t>131536</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>198582</t>
+          <t>198085</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15710,12 +15710,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15730,12 +15730,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>213502</t>
+          <t>213941</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>287232</t>
+          <t>288805</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15745,12 +15745,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -15773,12 +15773,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>192141</t>
+          <t>194783</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>238139</t>
+          <t>240820</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15788,12 +15788,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15808,12 +15808,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>289099</t>
+          <t>288652</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>462244</t>
+          <t>443167</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15823,12 +15823,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15843,12 +15843,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>505229</t>
+          <t>502104</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>670714</t>
+          <t>673057</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15858,12 +15858,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,47%</t>
         </is>
       </c>
     </row>
@@ -15886,12 +15886,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>130502</t>
+          <t>128660</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>172907</t>
+          <t>172246</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -15901,12 +15901,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -15921,12 +15921,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>173814</t>
+          <t>180743</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>279883</t>
+          <t>278765</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -15936,12 +15936,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -15956,12 +15956,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>324858</t>
+          <t>326940</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>436103</t>
+          <t>435559</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -15971,12 +15971,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,25%</t>
         </is>
       </c>
     </row>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>31918</t>
+          <t>33329</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -16014,12 +16014,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -16034,12 +16034,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6862</t>
+          <t>6777</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>21944</t>
+          <t>21004</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16049,12 +16049,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16069,12 +16069,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>13279</t>
+          <t>14105</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>47289</t>
+          <t>46614</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16084,12 +16084,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -16229,12 +16229,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>29547</t>
+          <t>32312</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16244,12 +16244,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16264,12 +16264,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>115050</t>
+          <t>117015</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>150576</t>
+          <t>153488</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16279,12 +16279,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16299,12 +16299,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>126122</t>
+          <t>126514</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>168816</t>
+          <t>171869</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16314,12 +16314,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -16342,12 +16342,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>45585</t>
+          <t>46022</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>92588</t>
+          <t>93556</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16357,12 +16357,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16377,12 +16377,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>241925</t>
+          <t>241704</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>286597</t>
+          <t>286171</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16392,12 +16392,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16412,12 +16412,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>300511</t>
+          <t>298332</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>367601</t>
+          <t>365829</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16427,12 +16427,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,36%</t>
         </is>
       </c>
     </row>
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>116255</t>
+          <t>117444</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>167644</t>
+          <t>167930</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16470,12 +16470,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16490,12 +16490,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>269480</t>
+          <t>272608</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>321990</t>
+          <t>323511</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16505,12 +16505,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16525,12 +16525,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>405348</t>
+          <t>399370</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>477691</t>
+          <t>477797</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16540,12 +16540,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,11%</t>
         </is>
       </c>
     </row>
@@ -16568,12 +16568,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>35444</t>
+          <t>35629</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16583,12 +16583,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16603,12 +16603,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13228</t>
+          <t>13262</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16618,12 +16618,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16638,12 +16638,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>20894</t>
+          <t>19822</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>58157</t>
+          <t>55392</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16653,12 +16653,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -16798,12 +16798,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>555851</t>
+          <t>558641</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1456579</t>
+          <t>1367032</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16813,12 +16813,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16833,12 +16833,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>564314</t>
+          <t>561824</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1271099</t>
+          <t>1215916</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16848,12 +16848,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16868,12 +16868,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1154898</t>
+          <t>1161610</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2272935</t>
+          <t>2277902</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16883,12 +16883,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,79%</t>
         </is>
       </c>
     </row>
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1015602</t>
+          <t>1052642</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1524130</t>
+          <t>1520525</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -16926,12 +16926,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -16946,12 +16946,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>942150</t>
+          <t>938634</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1270853</t>
+          <t>1275254</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -16961,12 +16961,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -16981,12 +16981,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2173966</t>
+          <t>2204691</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2727168</t>
+          <t>2734466</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -16996,12 +16996,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,56%</t>
         </is>
       </c>
     </row>
@@ -17024,12 +17024,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>844505</t>
+          <t>881637</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1237830</t>
+          <t>1239058</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17039,12 +17039,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17059,12 +17059,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1157287</t>
+          <t>1185135</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1562005</t>
+          <t>1573619</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17074,12 +17074,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17094,12 +17094,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2205336</t>
+          <t>2188357</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2755980</t>
+          <t>2760830</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17109,12 +17109,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,96%</t>
         </is>
       </c>
     </row>
@@ -17137,12 +17137,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>16771</t>
+          <t>17583</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>58736</t>
+          <t>65548</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17152,12 +17152,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17172,12 +17172,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>59624</t>
+          <t>56483</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>100047</t>
+          <t>99643</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17187,12 +17187,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17207,12 +17207,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>81462</t>
+          <t>82730</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>141129</t>
+          <t>138675</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17222,12 +17222,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
